--- a/data/trans_orig/KIDM_C_2_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_2_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60218</t>
+          <t>60925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66737</t>
+          <t>66862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88026</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>96837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152405</t>
+          <t>152213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162797</t>
+          <t>163043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137151</t>
+          <t>136989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142087</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168657</t>
+          <t>168479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>307825</t>
+          <t>308495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314174</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200011</t>
+          <t>199979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>208375</t>
+          <t>208436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260071</t>
+          <t>259755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269297</t>
+          <t>269356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>463375</t>
+          <t>463707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475939</t>
+          <t>475957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
